--- a/survey_templates/040_parent_roles_and_responsibilities_survey--survey_templates.xlsx
+++ b/survey_templates/040_parent_roles_and_responsibilities_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>introduction_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>introduction_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the highest level of education completed by the student’s parent(s)?</t>
+          <t>Parent Occupation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is your job title?</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How would you rate the student’s math skills?</t>
+          <t>Parent Science</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>parent_science</t>
+          <t>parent_science_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>parent_citizenship</t>
+          <t>parent_citizenship_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How would you rate the student’s citizenship skills?</t>
+          <t>Parent Citizenship 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,34 +1130,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>introduction_choices</t>
+          <t>introduction_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'elementary_school'}</t>
+          <t>elementary_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Elementary School'}</t>
+          <t>Elementary School</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>introduction_choices</t>
+          <t>introduction_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school_or_below'}</t>
+          <t>high_school_or_below</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High school or below'}</t>
+          <t>High school or below</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Some College'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bachelor’s_degree'}</t>
+          <t>bachelor’s_degree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bachelor’s degree'}</t>
+          <t>Bachelor’s degree</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'some_college_or_higher'}</t>
+          <t>some_college_or_higher</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Some college or higher'}</t>
+          <t>Some college or higher</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school_or_below'}</t>
+          <t>high_school_or_below</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High school or below'}</t>
+          <t>High school or below</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Some College'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bachelor’s_degree'}</t>
+          <t>bachelor’s_degree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bachelor’s degree'}</t>
+          <t>Bachelor’s degree</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'some_college_or_higher'}</t>
+          <t>some_college_or_higher</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Some college or higher'}</t>
+          <t>Some college or higher</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'math'}</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Math'}</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'social_studies'}</t>
+          <t>social_studies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Social Studies'}</t>
+          <t>Social Studies</t>
         </is>
       </c>
     </row>
